--- a/data/trans_dic/P43-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P43-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61,26%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>43,08%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>49,37%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,26%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,37; 51,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,11; 49,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,46; 54,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,05; 66,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,4; 52,02</t>
+          <t>40,37; 51,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,96; 48,75</t>
+          <t>37,11; 49,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,23; 55,17</t>
+          <t>44,46; 54,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,64; 66,23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40,4; 52,02</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>36,96; 48,75</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>44,23; 55,17</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>56,64; 66,23</t>
+          <t>56,05; 66,27</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>60,03%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>46,62%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>60,03%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,05; 35,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,51; 44,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,48; 52,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,11; 65,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,73; 36,5</t>
+          <t>26,05; 35,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,17; 44,87</t>
+          <t>33,51; 44,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,75; 51,99</t>
+          <t>41,48; 52,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,59; 64,68</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26,73; 36,5</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>33,17; 44,87</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>41,75; 51,99</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>54,59; 64,68</t>
+          <t>55,11; 65,81</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>64,49%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>52,09%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>64,49%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,89; 48,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,21; 58,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,34; 63,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,74; 71,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,23; 48,51</t>
+          <t>33,89; 48,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,12; 58,43</t>
+          <t>46,21; 58,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,39; 63,48</t>
+          <t>47,34; 63,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,57; 71,29</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>34,23; 48,51</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45,12; 58,43</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>48,39; 63,48</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>56,57; 71,29</t>
+          <t>56,74; 71,47</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62,98%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>33,35%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>39,69%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41,16%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,98%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,88; 36,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,13; 43,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,78; 44,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,39; 82,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,98; 36,82</t>
+          <t>29,88; 36,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,32; 43,57</t>
+          <t>36,13; 43,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,71; 44,99</t>
+          <t>37,78; 44,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,61; 86,0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29,98; 36,82</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>36,32; 43,57</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37,71; 44,99</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>48,61; 86,0</t>
+          <t>48,39; 82,84</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52,22%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>56,84%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>52,22%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,8; 40,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,92; 55,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,14; 60,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,95; 59,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,51; 40,26</t>
+          <t>31,8; 40,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,94; 55,66</t>
+          <t>47,92; 55,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,78; 60,61</t>
+          <t>53,14; 60,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,09; 60,23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>32,51; 40,26</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>47,94; 55,66</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>52,78; 60,61</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>36,09; 60,23</t>
+          <t>36,95; 59,57</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46,22%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>40,96%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>51,7%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>52,38%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>46,22%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,18; 43,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,58; 54,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,28; 55,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,58; 49,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,17; 43,79</t>
+          <t>38,18; 43,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,76; 54,82</t>
+          <t>48,58; 54,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,06; 55,33</t>
+          <t>49,28; 55,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,44; 50,06</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38,17; 43,79</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>48,76; 54,82</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>49,06; 55,33</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>42,44; 50,06</t>
+          <t>42,58; 49,87</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>37,92%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>47,15%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>49,95%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>56,16%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,29; 39,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,41; 48,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,18; 51,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,38; 66,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,18; 39,6</t>
+          <t>36,29; 39,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,42; 48,78</t>
+          <t>45,41; 48,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,19; 51,68</t>
+          <t>48,18; 51,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,16; 65,07</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>36,18; 39,6</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>45,42; 48,78</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>48,19; 51,68</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>51,16; 65,07</t>
+          <t>51,38; 66,59</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1308,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1647,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1660,22 +1343,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,20 +1362,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1737,26 +1408,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1773,10 +1424,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1791,22 +1438,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1825,26 +1472,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>327</t>
         </is>
@@ -1859,22 +1486,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140288</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135471</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1893,26 +1520,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>189108</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>140288</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>135471</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>170061</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>189108</t>
         </is>
@@ -1927,62 +1534,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>122946; 157999</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>116687; 154791</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>153130; 188996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>173007; 204545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>123063; 158433</t>
+          <t>122946; 157999</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116235; 153299</t>
+          <t>116687; 154791</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>152363; 190046</t>
+          <t>153130; 188996</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>174818; 204439</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>123063; 158433</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>116235; 153299</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>152363; 190046</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>174818; 204439</t>
+          <t>173007; 204545</t>
         </is>
       </c>
     </row>
@@ -1999,22 +1586,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2033,26 +1620,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>281</t>
         </is>
@@ -2067,22 +1634,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115302</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129727</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2101,26 +1668,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165764</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>115302</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>129727</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>172622</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>165764</t>
         </is>
@@ -2135,62 +1682,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96360; 132287</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>111479; 148654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>153603; 193279</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>152192; 181730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>98881; 135015</t>
+          <t>96360; 132287</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>110357; 149272</t>
+          <t>111479; 148654</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>154598; 192511</t>
+          <t>153603; 193279</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>150733; 178619</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>98881; 135015</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110357; 149272</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154598; 192511</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>150733; 178619</t>
+          <t>152192; 181730</t>
         </is>
       </c>
     </row>
@@ -2207,22 +1734,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2241,26 +1768,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>138</t>
         </is>
@@ -2275,22 +1782,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134417</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2309,26 +1816,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>76182</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>68501</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>134417</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>92972</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>76182</t>
         </is>
@@ -2343,62 +1830,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56522; 80508</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>119254; 150670</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>78647; 104914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67029; 84427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>57103; 80912</t>
+          <t>56522; 80508</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>116429; 150763</t>
+          <t>119254; 150670</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80379; 105449</t>
+          <t>78647; 104914</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66827; 84211</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>57103; 80912</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116429; 150763</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>80379; 105449</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>66827; 84211</t>
+          <t>67029; 84427</t>
         </is>
       </c>
     </row>
@@ -2415,22 +1882,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2449,26 +1916,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>507</t>
         </is>
@@ -2483,22 +1930,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>302624</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2517,26 +1964,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>480976</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>237292</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>302624</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>338774</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>480976</t>
         </is>
@@ -2551,62 +1978,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>212625; 262353</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>275535; 330960</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>310899; 368592</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>369513; 632643</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>213313; 262009</t>
+          <t>212625; 262353</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>276953; 332246</t>
+          <t>275535; 330960</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>310358; 370256</t>
+          <t>310899; 368592</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>371223; 656753</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>213313; 262009</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>276953; 332246</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>310358; 370256</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>371223; 656753</t>
+          <t>369513; 632643</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2030,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2657,26 +2064,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
@@ -2691,22 +2078,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204614</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>391154</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>417208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2725,26 +2112,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>355917</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>204614</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>391154</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>417208</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>355917</t>
         </is>
@@ -2759,62 +2126,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>180153; 227169</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>363004; 417369</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>390008; 445306</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>251837; 405959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>184190; 228093</t>
+          <t>180153; 227169</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>363171; 421621</t>
+          <t>363004; 417369</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>387358; 444845</t>
+          <t>390008; 445306</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>245944; 410465</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>184190; 228093</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>363171; 421621</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>387358; 444845</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>245944; 410465</t>
+          <t>251837; 405959</t>
         </is>
       </c>
     </row>
@@ -2831,22 +2178,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>502</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>531</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>545</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2865,26 +2212,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>545</t>
         </is>
@@ -2899,22 +2226,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>507445</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>570784</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>286186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2933,26 +2260,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>286186</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>507445</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>570784</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>559959</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>286186</t>
         </is>
@@ -2967,62 +2274,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>473089; 540262</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>536389; 606905</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>526843; 592718</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>263673; 308796</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>472880; 542512</t>
+          <t>473089; 540262</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>538307; 605260</t>
+          <t>536389; 606905</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>524412; 591514</t>
+          <t>526843; 592718</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>262819; 309977</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>472880; 542512</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>538307; 605260</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>524412; 591514</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>262819; 309977</t>
+          <t>263673; 308796</t>
         </is>
       </c>
     </row>
@@ -3039,22 +2326,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3073,26 +2360,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2415</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2415</t>
         </is>
@@ -3107,22 +2374,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273442</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1664177</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1751596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1554134</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3141,26 +2408,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1554134</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1273442</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1664177</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1751596</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>1554134</t>
         </is>
@@ -3175,62 +2422,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1218883; 1330341</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1602670; 1728341</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1689706; 1809311</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1421905; 1842768</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1215183; 1329841</t>
+          <t>1218883; 1330341</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1602990; 1721689</t>
+          <t>1602670; 1728341</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1690061; 1812290</t>
+          <t>1689706; 1809311</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1415761; 1800715</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1215183; 1329841</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1602990; 1721689</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1690061; 1812290</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1415761; 1800715</t>
+          <t>1421905; 1842768</t>
         </is>
       </c>
     </row>
@@ -3242,16 +2469,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P43-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P43-Clase-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,37; 51,87</t>
+          <t>40,72; 51,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,11; 49,23</t>
+          <t>37,55; 49,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,46; 54,87</t>
+          <t>43,86; 54,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,05; 66,27</t>
+          <t>56,98; 66,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,37; 51,87</t>
+          <t>40,72; 51,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,11; 49,23</t>
+          <t>37,55; 49,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,46; 54,87</t>
+          <t>43,86; 54,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,05; 66,27</t>
+          <t>56,98; 66,47</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,05; 35,76</t>
+          <t>26,63; 36,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,51; 44,69</t>
+          <t>33,05; 44,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,48; 52,2</t>
+          <t>41,07; 51,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,11; 65,81</t>
+          <t>54,45; 64,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,05; 35,76</t>
+          <t>26,63; 36,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,51; 44,69</t>
+          <t>33,05; 44,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,48; 52,2</t>
+          <t>41,07; 51,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,11; 65,81</t>
+          <t>54,45; 64,8</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,89; 48,27</t>
+          <t>33,62; 47,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 58,39</t>
+          <t>45,95; 58,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,34; 63,15</t>
+          <t>47,15; 63,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56,74; 71,47</t>
+          <t>55,0; 69,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,89; 48,27</t>
+          <t>33,62; 47,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 58,39</t>
+          <t>45,95; 58,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,34; 63,15</t>
+          <t>47,15; 63,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,74; 71,47</t>
+          <t>55,0; 69,4</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,88; 36,87</t>
+          <t>30,04; 37,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,13; 43,4</t>
+          <t>36,07; 43,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,78; 44,79</t>
+          <t>37,85; 44,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,39; 82,84</t>
+          <t>44,77; 51,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,88; 36,87</t>
+          <t>30,04; 37,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,13; 43,4</t>
+          <t>36,07; 43,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,78; 44,79</t>
+          <t>37,85; 44,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,39; 82,84</t>
+          <t>44,77; 51,56</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -1061,49 +1061,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,8; 40,1</t>
+          <t>32,17; 40,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,92; 55,1</t>
+          <t>48,17; 55,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,14; 60,67</t>
+          <t>53,47; 60,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,95; 59,57</t>
+          <t>50,34; 57,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,8; 40,1</t>
+          <t>32,17; 40,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,92; 55,1</t>
+          <t>48,17; 55,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,14; 60,67</t>
+          <t>53,47; 60,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,95; 59,57</t>
+          <t>50,34; 57,47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,18; 43,61</t>
+          <t>38,45; 43,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48,58; 54,97</t>
+          <t>48,75; 54,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,28; 55,45</t>
+          <t>49,02; 55,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42,58; 49,87</t>
+          <t>41,87; 49,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,18; 43,61</t>
+          <t>38,45; 43,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,58; 54,97</t>
+          <t>48,75; 54,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,28; 55,45</t>
+          <t>49,02; 55,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,58; 49,87</t>
+          <t>41,87; 49,04</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,29; 39,61</t>
+          <t>36,27; 39,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45,41; 48,97</t>
+          <t>45,3; 48,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,18; 51,6</t>
+          <t>48,27; 51,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51,38; 66,59</t>
+          <t>50,88; 54,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,29; 39,61</t>
+          <t>36,27; 39,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,41; 48,97</t>
+          <t>45,3; 48,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,18; 51,6</t>
+          <t>48,27; 51,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,38; 66,59</t>
+          <t>50,88; 54,36</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
     </row>
@@ -1534,42 +1534,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>122946; 157999</t>
+          <t>124041; 157053</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>116687; 154791</t>
+          <t>118092; 155208</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153130; 188996</t>
+          <t>151086; 188059</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>173007; 204545</t>
+          <t>192660; 224752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>122946; 157999</t>
+          <t>124041; 157053</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116687; 154791</t>
+          <t>118092; 155208</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>153130; 188996</t>
+          <t>151086; 188059</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>173007; 204545</t>
+          <t>192660; 224752</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
     </row>
@@ -1682,42 +1682,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>96360; 132287</t>
+          <t>98501; 134294</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111479; 148654</t>
+          <t>109945; 147766</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153603; 193279</t>
+          <t>152079; 190956</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152192; 181730</t>
+          <t>168269; 200255</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>96360; 132287</t>
+          <t>98501; 134294</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>111479; 148654</t>
+          <t>109945; 147766</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>153603; 193279</t>
+          <t>152079; 190956</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>152192; 181730</t>
+          <t>168269; 200255</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
     </row>
@@ -1830,42 +1830,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56522; 80508</t>
+          <t>56072; 79842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>119254; 150670</t>
+          <t>118579; 151502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78647; 104914</t>
+          <t>78326; 105229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67029; 84427</t>
+          <t>72271; 91199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56522; 80508</t>
+          <t>56072; 79842</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>119254; 150670</t>
+          <t>118579; 151502</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78647; 104914</t>
+          <t>78326; 105229</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>67029; 84427</t>
+          <t>72271; 91199</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
     </row>
@@ -1978,42 +1978,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>212625; 262353</t>
+          <t>213784; 263692</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275535; 330960</t>
+          <t>275050; 330937</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310899; 368592</t>
+          <t>311463; 368416</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>369513; 632643</t>
+          <t>279064; 321391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>212625; 262353</t>
+          <t>213784; 263692</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>275535; 330960</t>
+          <t>275050; 330937</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>310899; 368592</t>
+          <t>311463; 368416</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>369513; 632643</t>
+          <t>279064; 321391</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
     </row>
@@ -2126,49 +2126,49 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>180153; 227169</t>
+          <t>182255; 228880</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>363004; 417369</t>
+          <t>364882; 419991</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>390008; 445306</t>
+          <t>392440; 445644</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>251837; 405959</t>
+          <t>326336; 372537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>180153; 227169</t>
+          <t>182255; 228880</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>363004; 417369</t>
+          <t>364882; 419991</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>390008; 445306</t>
+          <t>392440; 445644</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>251837; 405959</t>
+          <t>326336; 372537</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286186</t>
+          <t>308336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>286186</t>
+          <t>308336</t>
         </is>
       </c>
     </row>
@@ -2274,42 +2274,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>473089; 540262</t>
+          <t>476402; 542098</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536389; 606905</t>
+          <t>538209; 604499</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>526843; 592718</t>
+          <t>524044; 593026</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>263673; 308796</t>
+          <t>285224; 334059</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>473089; 540262</t>
+          <t>476402; 542098</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>536389; 606905</t>
+          <t>538209; 604499</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>526843; 592718</t>
+          <t>524044; 593026</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>263673; 308796</t>
+          <t>285224; 334059</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1554134</t>
+          <t>1434237</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1554134</t>
+          <t>1434237</t>
         </is>
       </c>
     </row>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1218883; 1330341</t>
+          <t>1218012; 1330056</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1602670; 1728341</t>
+          <t>1598664; 1720806</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1689706; 1809311</t>
+          <t>1692839; 1811021</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1421905; 1842768</t>
+          <t>1389628; 1484717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1218883; 1330341</t>
+          <t>1218012; 1330056</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1602670; 1728341</t>
+          <t>1598664; 1720806</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1689706; 1809311</t>
+          <t>1692839; 1811021</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1421905; 1842768</t>
+          <t>1389628; 1484717</t>
         </is>
       </c>
     </row>
